--- a/pandas_programs/Basic Excel.xlsx
+++ b/pandas_programs/Basic Excel.xlsx
@@ -5,15 +5,16 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\notes\Data Analysis\MArgi DA\Excel work\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\notes\Data Analysis\python_DA\pandas_programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77542673-AEDD-47A9-AB74-BF3B4E4E3337}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A504527A-3A21-4FFA-8C66-F22591959388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
   <si>
     <t>sno</t>
   </si>
@@ -115,6 +116,9 @@
   </si>
   <si>
     <t>IF(AND(E8&gt;34,F8&gt;32,G8&gt;32),"Pass","Fail")</t>
+  </si>
+  <si>
+    <t>Abs</t>
   </si>
 </sst>
 </file>
@@ -864,4 +868,400 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F17B8AF-37F3-4ACC-961F-28B51D7F2CC2}">
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <f>_xlfn.CONCAT(B2," ",C2)</f>
+        <v>Aman sharma</v>
+      </c>
+      <c r="E2" s="1">
+        <v>35</v>
+      </c>
+      <c r="F2" s="1">
+        <v>45</v>
+      </c>
+      <c r="G2" s="1">
+        <v>37</v>
+      </c>
+      <c r="H2" s="1" t="str">
+        <f>IF(AND(E2&gt;34,F2&gt;32,G2&gt;32),"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="I2" s="2">
+        <f>IF(H2="Pass", AVERAGE(E2:G2)/100,H2)</f>
+        <v>0.39</v>
+      </c>
+      <c r="J2" s="1" t="str">
+        <f>IF(I2="Fail",I2,IF(I2&gt;65%,"Ist division",IF(I2&gt;44%,"IInd Division","IIIrdDivision")))</f>
+        <v>IIIrdDivision</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="str">
+        <f t="shared" ref="D3:D11" si="0">_xlfn.CONCAT(B3," ",C3)</f>
+        <v xml:space="preserve">Raman </v>
+      </c>
+      <c r="E3" s="1">
+        <v>85</v>
+      </c>
+      <c r="F3" s="1">
+        <v>88</v>
+      </c>
+      <c r="G3" s="1">
+        <v>78</v>
+      </c>
+      <c r="H3" s="1" t="str">
+        <f t="shared" ref="H3:H11" si="1">IF(AND(E3&gt;34,F3&gt;32,G3&gt;32),"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="I3" s="2">
+        <f t="shared" ref="I3:I11" si="2">IF(H3="Pass", AVERAGE(E3:G3)/100,H3)</f>
+        <v>0.83666666666666667</v>
+      </c>
+      <c r="J3" s="1" t="str">
+        <f t="shared" ref="J3:J11" si="3">IF(I3="Fail",I3,IF(I3&gt;65%,"Ist division",IF(I3&gt;44%,"IInd Division","IIIrdDivision")))</f>
+        <v>Ist division</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>John capner</v>
+      </c>
+      <c r="E4" s="1">
+        <v>25</v>
+      </c>
+      <c r="F4" s="1">
+        <v>36</v>
+      </c>
+      <c r="G4" s="1">
+        <v>41</v>
+      </c>
+      <c r="H4" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+      <c r="I4" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Fail</v>
+      </c>
+      <c r="J4" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Ron capner</v>
+      </c>
+      <c r="E5" s="1">
+        <v>58</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="1">
+        <v>45</v>
+      </c>
+      <c r="H5" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+      <c r="I5" s="2">
+        <f t="shared" si="2"/>
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="J5" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>IInd Division</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Maria dsoza</v>
+      </c>
+      <c r="E6" s="1">
+        <v>74</v>
+      </c>
+      <c r="F6" s="1">
+        <v>58</v>
+      </c>
+      <c r="G6" s="1">
+        <v>65</v>
+      </c>
+      <c r="H6" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+      <c r="I6" s="2">
+        <f t="shared" si="2"/>
+        <v>0.65666666666666673</v>
+      </c>
+      <c r="J6" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>Ist division</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">Tania </v>
+      </c>
+      <c r="E7" s="1">
+        <v>25</v>
+      </c>
+      <c r="F7" s="1">
+        <v>12</v>
+      </c>
+      <c r="G7" s="1">
+        <v>32</v>
+      </c>
+      <c r="H7" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+      <c r="I7" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Fail</v>
+      </c>
+      <c r="J7" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Sam daneil</v>
+      </c>
+      <c r="E8" s="1">
+        <v>78</v>
+      </c>
+      <c r="F8" s="1">
+        <v>98</v>
+      </c>
+      <c r="G8" s="1">
+        <v>96</v>
+      </c>
+      <c r="H8" s="1" t="str">
+        <f>IF(AND(E8&gt;34,F8&gt;32,G8&gt;32),"Pass","Fail")</f>
+        <v>Pass</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="2"/>
+        <v>0.90666666666666673</v>
+      </c>
+      <c r="J8" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>Ist division</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Alexa patel</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <v>56</v>
+      </c>
+      <c r="G9" s="1">
+        <v>45</v>
+      </c>
+      <c r="H9" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Fail</v>
+      </c>
+      <c r="I9" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Fail</v>
+      </c>
+      <c r="J9" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>Fail</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>Joseph j</v>
+      </c>
+      <c r="E10" s="1">
+        <v>75</v>
+      </c>
+      <c r="F10" s="1">
+        <v>65</v>
+      </c>
+      <c r="G10" s="1">
+        <v>69</v>
+      </c>
+      <c r="H10" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="2"/>
+        <v>0.69666666666666677</v>
+      </c>
+      <c r="J10" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>Ist division</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="21" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <f t="shared" si="0"/>
+        <v>arun chawda</v>
+      </c>
+      <c r="E11" s="1">
+        <v>78</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="1">
+        <v>85</v>
+      </c>
+      <c r="H11" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>Pass</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="2"/>
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="J11" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>Ist division</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/pandas_programs/Basic Excel.xlsx
+++ b/pandas_programs/Basic Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\notes\Data Analysis\python_DA\pandas_programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A504527A-3A21-4FFA-8C66-F22591959388}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79D44B32-DBE8-4611-860A-73E9C07B1363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="30">
   <si>
     <t>sno</t>
   </si>
@@ -116,9 +116,6 @@
   </si>
   <si>
     <t>IF(AND(E8&gt;34,F8&gt;32,G8&gt;32),"Pass","Fail")</t>
-  </si>
-  <si>
-    <t>Abs</t>
   </si>
 </sst>
 </file>
@@ -1030,23 +1027,23 @@
       <c r="E5" s="1">
         <v>58</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>30</v>
+      <c r="F5" s="1">
+        <v>0</v>
       </c>
       <c r="G5" s="1">
         <v>45</v>
       </c>
       <c r="H5" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Pass</v>
-      </c>
-      <c r="I5" s="2">
-        <f t="shared" si="2"/>
-        <v>0.51500000000000001</v>
+        <v>Fail</v>
+      </c>
+      <c r="I5" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Fail</v>
       </c>
       <c r="J5" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>IInd Division</v>
+        <v>Fail</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="21" x14ac:dyDescent="0.25">
@@ -1169,12 +1166,14 @@
         <f t="shared" si="0"/>
         <v>Alexa patel</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
       <c r="F9" s="1">
         <v>56</v>
       </c>
       <c r="G9" s="1">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="H9" s="1" t="str">
         <f t="shared" si="1"/>
@@ -1242,23 +1241,23 @@
       <c r="E11" s="1">
         <v>78</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>30</v>
+      <c r="F11" s="1">
+        <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>85</v>
       </c>
       <c r="H11" s="1" t="str">
         <f t="shared" si="1"/>
-        <v>Pass</v>
-      </c>
-      <c r="I11" s="2">
-        <f t="shared" si="2"/>
-        <v>0.81499999999999995</v>
+        <v>Fail</v>
+      </c>
+      <c r="I11" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v>Fail</v>
       </c>
       <c r="J11" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>Ist division</v>
+        <v>Fail</v>
       </c>
     </row>
   </sheetData>
